--- a/src/test/resources/testData/Event.xlsx
+++ b/src/test/resources/testData/Event.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="40">
   <si>
     <t>SKU</t>
   </si>
@@ -65,10 +65,13 @@
     <t>isCustomerEnv</t>
   </si>
   <si>
+    <t>Related_Product_Family</t>
+  </si>
+  <si>
     <t>Etkinlik Adı</t>
   </si>
   <si>
-    <t>f1c3baaa-c96d-4166-bcda-7d30f7257f16</t>
+    <t>5a3dafc1-d230-4e11-8207-20e343dbca71</t>
   </si>
   <si>
     <t>Kurumsal İletişim</t>
@@ -80,13 +83,13 @@
     <t>Option1</t>
   </si>
   <si>
-    <t>a4c9f46e-df05-49ce-81d8-2ec5946fb3af</t>
+    <t>096ea0f4-5dac-4af2-84b5-ca5487ebc070</t>
   </si>
   <si>
     <t>ROOT</t>
   </si>
   <si>
-    <t>18.02.2026</t>
+    <t>24.02.2026</t>
   </si>
   <si>
     <t>Doğru</t>
@@ -95,13 +98,13 @@
     <t>Option2</t>
   </si>
   <si>
-    <t>56815bb8-bb1c-4186-bb9a-fb87d0bb9d56</t>
+    <t>adc7ca5e-5ae2-4167-a32f-58ba94578313</t>
   </si>
   <si>
     <t>Tümü</t>
   </si>
   <si>
-    <t>ad7bf66c-1029-4e7b-9688-e290195e2856</t>
+    <t>d7e49e6c-40ee-40fb-8938-e18f2e20d1ec</t>
   </si>
   <si>
     <t>Yanlış</t>
@@ -110,7 +113,7 @@
     <t>Option3</t>
   </si>
   <si>
-    <t>838bef50-fdfd-4dbd-8ef4-62623599c933</t>
+    <t>7910836e-f134-4ab1-846e-43d993444a7e</t>
   </si>
   <si>
     <t>Konferans</t>
@@ -119,10 +122,10 @@
     <t>Event-04</t>
   </si>
   <si>
-    <t>0e409ae9-0cb2-4b19-bf1a-3d4282e882e3</t>
-  </si>
-  <si>
-    <t>16.02.2026</t>
+    <t>ff63e71b-a81b-4370-b64d-ac861957387f</t>
+  </si>
+  <si>
+    <t>22.02.2026</t>
   </si>
   <si>
     <t>Event-08</t>
@@ -178,7 +181,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:Q8"/>
+  <dimension ref="A1:R8"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -216,7 +219,7 @@
         <v>10</v>
       </c>
       <c r="L1" t="s" s="0">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M1" t="s" s="0">
         <v>12</v>
@@ -233,106 +236,109 @@
       <c r="Q1" t="s" s="0">
         <v>16</v>
       </c>
+      <c r="R1" t="s" s="0">
+        <v>17</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F2" t="s" s="0">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G2" t="s" s="0">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E3" t="s" s="0">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G3" t="s" s="0">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H3" t="n" s="1">
-        <v>46071.0</v>
+        <v>46077.0</v>
       </c>
     </row>
     <row r="4">
       <c r="C4" t="s" s="0">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L4" t="s" s="0">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5">
       <c r="B5" t="s" s="0">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E5" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="G5" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="L5" t="s" s="0">
         <v>30</v>
-      </c>
-      <c r="G5" t="s" s="0">
-        <v>31</v>
-      </c>
-      <c r="L5" t="s" s="0">
-        <v>29</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D6" t="s" s="0">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L6" t="s" s="0">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="P6" t="s" s="0">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C7" t="s" s="0">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L7" t="s" s="0">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="N7" t="n" s="2">
-        <v>46071.0</v>
+        <v>46077.0</v>
       </c>
       <c r="O7" t="n" s="3">
-        <v>46069.0</v>
+        <v>46075.0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L8" t="s" s="0">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>

--- a/src/test/resources/testData/Event.xlsx
+++ b/src/test/resources/testData/Event.xlsx
@@ -71,7 +71,7 @@
     <t>Etkinlik Adı</t>
   </si>
   <si>
-    <t>5a3dafc1-d230-4e11-8207-20e343dbca71</t>
+    <t>8e5dffa4-0a70-48de-9f58-91d7858b6715</t>
   </si>
   <si>
     <t>Kurumsal İletişim</t>
@@ -83,37 +83,37 @@
     <t>Option1</t>
   </si>
   <si>
-    <t>096ea0f4-5dac-4af2-84b5-ca5487ebc070</t>
+    <t>7a9d1415-7b43-45b9-8d00-909fbf33fd16</t>
+  </si>
+  <si>
+    <t>Tümü</t>
+  </si>
+  <si>
+    <t>20.03.2026</t>
+  </si>
+  <si>
+    <t>Doğru</t>
+  </si>
+  <si>
+    <t>Option2</t>
+  </si>
+  <si>
+    <t>a8c90e58-45d8-421e-a4c9-0805ba8ef175</t>
+  </si>
+  <si>
+    <t>1bc977b7-57dd-4879-88e2-ad8c8306c966</t>
+  </si>
+  <si>
+    <t>Yanlış</t>
+  </si>
+  <si>
+    <t>Option3</t>
   </si>
   <si>
     <t>ROOT</t>
   </si>
   <si>
-    <t>24.02.2026</t>
-  </si>
-  <si>
-    <t>Doğru</t>
-  </si>
-  <si>
-    <t>Option2</t>
-  </si>
-  <si>
-    <t>adc7ca5e-5ae2-4167-a32f-58ba94578313</t>
-  </si>
-  <si>
-    <t>Tümü</t>
-  </si>
-  <si>
-    <t>d7e49e6c-40ee-40fb-8938-e18f2e20d1ec</t>
-  </si>
-  <si>
-    <t>Yanlış</t>
-  </si>
-  <si>
-    <t>Option3</t>
-  </si>
-  <si>
-    <t>7910836e-f134-4ab1-846e-43d993444a7e</t>
+    <t>2c542705-04a5-4063-9954-c706fc1b4c9b</t>
   </si>
   <si>
     <t>Konferans</t>
@@ -122,10 +122,10 @@
     <t>Event-04</t>
   </si>
   <si>
-    <t>ff63e71b-a81b-4370-b64d-ac861957387f</t>
-  </si>
-  <si>
-    <t>22.02.2026</t>
+    <t>c5bdf207-9165-4ac0-932b-fd2dbcc3d5dc</t>
+  </si>
+  <si>
+    <t>18.03.2026</t>
   </si>
   <si>
     <t>Event-08</t>
@@ -268,7 +268,7 @@
         <v>27</v>
       </c>
       <c r="H3" t="n" s="1">
-        <v>46077.0</v>
+        <v>46101.0</v>
       </c>
     </row>
     <row r="4">
@@ -281,16 +281,16 @@
     </row>
     <row r="5">
       <c r="B5" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="E5" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="G5" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="L5" t="s" s="0">
         <v>29</v>
-      </c>
-      <c r="E5" t="s" s="0">
-        <v>31</v>
-      </c>
-      <c r="G5" t="s" s="0">
-        <v>32</v>
-      </c>
-      <c r="L5" t="s" s="0">
-        <v>30</v>
       </c>
     </row>
     <row r="6">
@@ -298,13 +298,13 @@
         <v>33</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="C6" t="s" s="0">
         <v>20</v>
       </c>
       <c r="D6" t="s" s="0">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L6" t="s" s="0">
         <v>33</v>
@@ -327,10 +327,10 @@
         <v>36</v>
       </c>
       <c r="N7" t="n" s="2">
-        <v>46077.0</v>
+        <v>46101.0</v>
       </c>
       <c r="O7" t="n" s="3">
-        <v>46075.0</v>
+        <v>46099.0</v>
       </c>
     </row>
     <row r="8">

--- a/src/test/resources/testData/Event.xlsx
+++ b/src/test/resources/testData/Event.xlsx
@@ -71,7 +71,7 @@
     <t>Etkinlik Adı</t>
   </si>
   <si>
-    <t>8e5dffa4-0a70-48de-9f58-91d7858b6715</t>
+    <t>39402678-df1d-4698-990a-dea1eb1d4336</t>
   </si>
   <si>
     <t>Kurumsal İletişim</t>
@@ -83,13 +83,13 @@
     <t>Option1</t>
   </si>
   <si>
-    <t>7a9d1415-7b43-45b9-8d00-909fbf33fd16</t>
+    <t>67d8b7a7-b803-4298-b3e9-a519a17fa21f</t>
   </si>
   <si>
     <t>Tümü</t>
   </si>
   <si>
-    <t>20.03.2026</t>
+    <t>25.03.2026</t>
   </si>
   <si>
     <t>Doğru</t>
@@ -98,10 +98,10 @@
     <t>Option2</t>
   </si>
   <si>
-    <t>a8c90e58-45d8-421e-a4c9-0805ba8ef175</t>
-  </si>
-  <si>
-    <t>1bc977b7-57dd-4879-88e2-ad8c8306c966</t>
+    <t>47cd5fba-d97c-4b4f-8e8d-7c1aef8b921a</t>
+  </si>
+  <si>
+    <t>64871039-6bce-4a2d-b9c3-018aa75fa64c</t>
   </si>
   <si>
     <t>Yanlış</t>
@@ -113,7 +113,7 @@
     <t>ROOT</t>
   </si>
   <si>
-    <t>2c542705-04a5-4063-9954-c706fc1b4c9b</t>
+    <t>76a158a0-a3ba-4f0b-a940-1b86b76d3562</t>
   </si>
   <si>
     <t>Konferans</t>
@@ -122,10 +122,10 @@
     <t>Event-04</t>
   </si>
   <si>
-    <t>c5bdf207-9165-4ac0-932b-fd2dbcc3d5dc</t>
-  </si>
-  <si>
-    <t>18.03.2026</t>
+    <t>348a430a-d71c-4a12-b894-72dbf96c408d</t>
+  </si>
+  <si>
+    <t>23.03.2026</t>
   </si>
   <si>
     <t>Event-08</t>
@@ -268,7 +268,7 @@
         <v>27</v>
       </c>
       <c r="H3" t="n" s="1">
-        <v>46101.0</v>
+        <v>46106.0</v>
       </c>
     </row>
     <row r="4">
@@ -327,10 +327,10 @@
         <v>36</v>
       </c>
       <c r="N7" t="n" s="2">
-        <v>46101.0</v>
+        <v>46106.0</v>
       </c>
       <c r="O7" t="n" s="3">
-        <v>46099.0</v>
+        <v>46104.0</v>
       </c>
     </row>
     <row r="8">

--- a/src/test/resources/testData/Event.xlsx
+++ b/src/test/resources/testData/Event.xlsx
@@ -71,7 +71,7 @@
     <t>Etkinlik Adı</t>
   </si>
   <si>
-    <t>39402678-df1d-4698-990a-dea1eb1d4336</t>
+    <t>12ef1a15-8537-4c80-aadf-c7fe31a84715</t>
   </si>
   <si>
     <t>Kurumsal İletişim</t>
@@ -83,13 +83,13 @@
     <t>Option1</t>
   </si>
   <si>
-    <t>67d8b7a7-b803-4298-b3e9-a519a17fa21f</t>
+    <t>a13284fd-a9bc-4fc5-8787-a4b2fae14546</t>
   </si>
   <si>
     <t>Tümü</t>
   </si>
   <si>
-    <t>25.03.2026</t>
+    <t>07.04.2026</t>
   </si>
   <si>
     <t>Doğru</t>
@@ -98,10 +98,10 @@
     <t>Option2</t>
   </si>
   <si>
-    <t>47cd5fba-d97c-4b4f-8e8d-7c1aef8b921a</t>
-  </si>
-  <si>
-    <t>64871039-6bce-4a2d-b9c3-018aa75fa64c</t>
+    <t>0ffe096e-17e6-4da1-83ba-aa13c1ff3e6d</t>
+  </si>
+  <si>
+    <t>6d674339-105e-4e99-b36d-73992a88706b</t>
   </si>
   <si>
     <t>Yanlış</t>
@@ -113,7 +113,7 @@
     <t>ROOT</t>
   </si>
   <si>
-    <t>76a158a0-a3ba-4f0b-a940-1b86b76d3562</t>
+    <t>24bb1299-bd46-482b-9c85-bd8a90ca9e1b</t>
   </si>
   <si>
     <t>Konferans</t>
@@ -122,10 +122,10 @@
     <t>Event-04</t>
   </si>
   <si>
-    <t>348a430a-d71c-4a12-b894-72dbf96c408d</t>
-  </si>
-  <si>
-    <t>23.03.2026</t>
+    <t>fe8acf18-8285-47dc-b22d-4a81131348c6</t>
+  </si>
+  <si>
+    <t>05.04.2026</t>
   </si>
   <si>
     <t>Event-08</t>
@@ -268,7 +268,7 @@
         <v>27</v>
       </c>
       <c r="H3" t="n" s="1">
-        <v>46106.0</v>
+        <v>46119.0</v>
       </c>
     </row>
     <row r="4">
@@ -327,10 +327,10 @@
         <v>36</v>
       </c>
       <c r="N7" t="n" s="2">
-        <v>46106.0</v>
+        <v>46119.0</v>
       </c>
       <c r="O7" t="n" s="3">
-        <v>46104.0</v>
+        <v>46117.0</v>
       </c>
     </row>
     <row r="8">

--- a/src/test/resources/testData/Event.xlsx
+++ b/src/test/resources/testData/Event.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="41">
   <si>
     <t>SKU</t>
   </si>
@@ -38,6 +38,9 @@
     <t>NewDate</t>
   </si>
   <si>
+    <t>E-Posta</t>
+  </si>
+  <si>
     <t>City_Roof</t>
   </si>
   <si>
@@ -71,7 +74,7 @@
     <t>Etkinlik Adı</t>
   </si>
   <si>
-    <t>12ef1a15-8537-4c80-aadf-c7fe31a84715</t>
+    <t>134303ea-8283-463e-9f37-4c234fe5e352</t>
   </si>
   <si>
     <t>Kurumsal İletişim</t>
@@ -83,13 +86,13 @@
     <t>Option1</t>
   </si>
   <si>
-    <t>a13284fd-a9bc-4fc5-8787-a4b2fae14546</t>
+    <t>871133d8-5d5a-4125-8a66-95f6b8ba5b15</t>
   </si>
   <si>
     <t>Tümü</t>
   </si>
   <si>
-    <t>07.04.2026</t>
+    <t>18.04.2026</t>
   </si>
   <si>
     <t>Doğru</t>
@@ -98,10 +101,10 @@
     <t>Option2</t>
   </si>
   <si>
-    <t>0ffe096e-17e6-4da1-83ba-aa13c1ff3e6d</t>
-  </si>
-  <si>
-    <t>6d674339-105e-4e99-b36d-73992a88706b</t>
+    <t>22cdbaff-f244-4a2c-bedc-4442ff46f3d2</t>
+  </si>
+  <si>
+    <t>f157402b-9faa-4015-9cc7-8e5c5f04c6d6</t>
   </si>
   <si>
     <t>Yanlış</t>
@@ -113,7 +116,7 @@
     <t>ROOT</t>
   </si>
   <si>
-    <t>24bb1299-bd46-482b-9c85-bd8a90ca9e1b</t>
+    <t>5fe1daac-e5cc-4974-bdcd-a593f1a8da49</t>
   </si>
   <si>
     <t>Konferans</t>
@@ -122,10 +125,10 @@
     <t>Event-04</t>
   </si>
   <si>
-    <t>fe8acf18-8285-47dc-b22d-4a81131348c6</t>
-  </si>
-  <si>
-    <t>05.04.2026</t>
+    <t>2b29ce58-8ac3-4871-b9eb-83ba8218c5e8</t>
+  </si>
+  <si>
+    <t>16.04.2026</t>
   </si>
   <si>
     <t>Event-08</t>
@@ -210,135 +213,135 @@
         <v>7</v>
       </c>
       <c r="I1" t="s" s="0">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J1" t="s" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K1" t="s" s="0">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L1" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="M1" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="N1" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="O1" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="P1" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="Q1" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="R1" t="s" s="0">
         <v>18</v>
-      </c>
-      <c r="M1" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="N1" t="s" s="0">
-        <v>13</v>
-      </c>
-      <c r="O1" t="s" s="0">
-        <v>14</v>
-      </c>
-      <c r="P1" t="s" s="0">
-        <v>15</v>
-      </c>
-      <c r="Q1" t="s" s="0">
-        <v>16</v>
-      </c>
-      <c r="R1" t="s" s="0">
-        <v>17</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F2" t="s" s="0">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G2" t="s" s="0">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E3" t="s" s="0">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G3" t="s" s="0">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H3" t="n" s="1">
-        <v>46119.0</v>
+        <v>46130.0</v>
       </c>
     </row>
     <row r="4">
       <c r="C4" t="s" s="0">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L4" t="s" s="0">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5">
       <c r="B5" t="s" s="0">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E5" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="G5" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="L5" t="s" s="0">
         <v>30</v>
-      </c>
-      <c r="G5" t="s" s="0">
-        <v>31</v>
-      </c>
-      <c r="L5" t="s" s="0">
-        <v>29</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="B6" t="s" s="0">
         <v>33</v>
       </c>
-      <c r="B6" t="s" s="0">
-        <v>32</v>
-      </c>
       <c r="C6" t="s" s="0">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D6" t="s" s="0">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L6" t="s" s="0">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P6" t="s" s="0">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C7" t="s" s="0">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L7" t="s" s="0">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="N7" t="n" s="2">
-        <v>46119.0</v>
+        <v>46130.0</v>
       </c>
       <c r="O7" t="n" s="3">
-        <v>46117.0</v>
+        <v>46128.0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L8" t="s" s="0">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/src/test/resources/testData/Event.xlsx
+++ b/src/test/resources/testData/Event.xlsx
@@ -74,7 +74,7 @@
     <t>Etkinlik Adı</t>
   </si>
   <si>
-    <t>134303ea-8283-463e-9f37-4c234fe5e352</t>
+    <t>89058b4d-a0f8-4672-bb67-ce8f34ee4b39</t>
   </si>
   <si>
     <t>Kurumsal İletişim</t>
@@ -86,13 +86,13 @@
     <t>Option1</t>
   </si>
   <si>
-    <t>871133d8-5d5a-4125-8a66-95f6b8ba5b15</t>
+    <t>713d68f2-cd89-4919-bb57-6974dae72beb</t>
   </si>
   <si>
     <t>Tümü</t>
   </si>
   <si>
-    <t>18.04.2026</t>
+    <t>21.04.2026</t>
   </si>
   <si>
     <t>Doğru</t>
@@ -101,10 +101,10 @@
     <t>Option2</t>
   </si>
   <si>
-    <t>22cdbaff-f244-4a2c-bedc-4442ff46f3d2</t>
-  </si>
-  <si>
-    <t>f157402b-9faa-4015-9cc7-8e5c5f04c6d6</t>
+    <t>ebf4ef3f-d14f-438f-b50c-80d5cfa11576</t>
+  </si>
+  <si>
+    <t>20fd1192-5a7d-425f-b586-9255d4e0ec94</t>
   </si>
   <si>
     <t>Yanlış</t>
@@ -116,7 +116,7 @@
     <t>ROOT</t>
   </si>
   <si>
-    <t>5fe1daac-e5cc-4974-bdcd-a593f1a8da49</t>
+    <t>ed0b394b-4616-4b76-b3db-cde53a21b164</t>
   </si>
   <si>
     <t>Konferans</t>
@@ -125,10 +125,10 @@
     <t>Event-04</t>
   </si>
   <si>
-    <t>2b29ce58-8ac3-4871-b9eb-83ba8218c5e8</t>
-  </si>
-  <si>
-    <t>16.04.2026</t>
+    <t>d2f76a7d-b2c9-4d9f-9b57-dd818635068c</t>
+  </si>
+  <si>
+    <t>19.04.2026</t>
   </si>
   <si>
     <t>Event-08</t>
@@ -271,7 +271,7 @@
         <v>28</v>
       </c>
       <c r="H3" t="n" s="1">
-        <v>46130.0</v>
+        <v>46133.0</v>
       </c>
     </row>
     <row r="4">
@@ -330,10 +330,10 @@
         <v>37</v>
       </c>
       <c r="N7" t="n" s="2">
-        <v>46130.0</v>
+        <v>46133.0</v>
       </c>
       <c r="O7" t="n" s="3">
-        <v>46128.0</v>
+        <v>46131.0</v>
       </c>
     </row>
     <row r="8">

--- a/src/test/resources/testData/Event.xlsx
+++ b/src/test/resources/testData/Event.xlsx
@@ -74,7 +74,7 @@
     <t>Etkinlik Adı</t>
   </si>
   <si>
-    <t>89058b4d-a0f8-4672-bb67-ce8f34ee4b39</t>
+    <t>93173474-dd24-4d6a-b201-da244bf44d5c</t>
   </si>
   <si>
     <t>Kurumsal İletişim</t>
@@ -86,13 +86,13 @@
     <t>Option1</t>
   </si>
   <si>
-    <t>713d68f2-cd89-4919-bb57-6974dae72beb</t>
+    <t>0d2d4876-8e57-49b0-ac98-a661bccc2d26</t>
   </si>
   <si>
     <t>Tümü</t>
   </si>
   <si>
-    <t>21.04.2026</t>
+    <t>01.05.2026</t>
   </si>
   <si>
     <t>Doğru</t>
@@ -101,10 +101,10 @@
     <t>Option2</t>
   </si>
   <si>
-    <t>ebf4ef3f-d14f-438f-b50c-80d5cfa11576</t>
-  </si>
-  <si>
-    <t>20fd1192-5a7d-425f-b586-9255d4e0ec94</t>
+    <t>61c93d57-7dfc-4841-9ef9-fcb16196865a</t>
+  </si>
+  <si>
+    <t>1df98e06-1c77-490b-8f94-0d025d037bf6</t>
   </si>
   <si>
     <t>Yanlış</t>
@@ -116,7 +116,7 @@
     <t>ROOT</t>
   </si>
   <si>
-    <t>ed0b394b-4616-4b76-b3db-cde53a21b164</t>
+    <t>97f6c106-906c-4a80-9b54-a75c5f54a172</t>
   </si>
   <si>
     <t>Konferans</t>
@@ -125,10 +125,10 @@
     <t>Event-04</t>
   </si>
   <si>
-    <t>d2f76a7d-b2c9-4d9f-9b57-dd818635068c</t>
-  </si>
-  <si>
-    <t>19.04.2026</t>
+    <t>465629c8-9270-431d-b890-f3b852fdff75</t>
+  </si>
+  <si>
+    <t>29.04.2026</t>
   </si>
   <si>
     <t>Event-08</t>
@@ -271,7 +271,7 @@
         <v>28</v>
       </c>
       <c r="H3" t="n" s="1">
-        <v>46133.0</v>
+        <v>46143.0</v>
       </c>
     </row>
     <row r="4">
@@ -330,10 +330,10 @@
         <v>37</v>
       </c>
       <c r="N7" t="n" s="2">
-        <v>46133.0</v>
+        <v>46143.0</v>
       </c>
       <c r="O7" t="n" s="3">
-        <v>46131.0</v>
+        <v>46141.0</v>
       </c>
     </row>
     <row r="8">

--- a/src/test/resources/testData/Event.xlsx
+++ b/src/test/resources/testData/Event.xlsx
@@ -74,7 +74,7 @@
     <t>Etkinlik Adı</t>
   </si>
   <si>
-    <t>93173474-dd24-4d6a-b201-da244bf44d5c</t>
+    <t>e4e513ea-95d2-44a6-ac3d-5982bcfba88b</t>
   </si>
   <si>
     <t>Kurumsal İletişim</t>
@@ -86,13 +86,13 @@
     <t>Option1</t>
   </si>
   <si>
-    <t>0d2d4876-8e57-49b0-ac98-a661bccc2d26</t>
+    <t>705dcd44-4baa-4e2b-b2f5-7eca1ba22fd6</t>
   </si>
   <si>
     <t>Tümü</t>
   </si>
   <si>
-    <t>01.05.2026</t>
+    <t>05.05.2026</t>
   </si>
   <si>
     <t>Doğru</t>
@@ -101,10 +101,10 @@
     <t>Option2</t>
   </si>
   <si>
-    <t>61c93d57-7dfc-4841-9ef9-fcb16196865a</t>
-  </si>
-  <si>
-    <t>1df98e06-1c77-490b-8f94-0d025d037bf6</t>
+    <t>b203b61d-628c-4b67-9043-957b49d2f2c2</t>
+  </si>
+  <si>
+    <t>5d64d255-502a-4d88-9edf-0fd3732b6406</t>
   </si>
   <si>
     <t>Yanlış</t>
@@ -116,7 +116,7 @@
     <t>ROOT</t>
   </si>
   <si>
-    <t>97f6c106-906c-4a80-9b54-a75c5f54a172</t>
+    <t>1d413ece-1aed-4a99-b319-fe90747aeb93</t>
   </si>
   <si>
     <t>Konferans</t>
@@ -125,10 +125,10 @@
     <t>Event-04</t>
   </si>
   <si>
-    <t>465629c8-9270-431d-b890-f3b852fdff75</t>
-  </si>
-  <si>
-    <t>29.04.2026</t>
+    <t>9914a215-179d-4afe-a438-088effe1684b</t>
+  </si>
+  <si>
+    <t>03.05.2026</t>
   </si>
   <si>
     <t>Event-08</t>
@@ -271,7 +271,7 @@
         <v>28</v>
       </c>
       <c r="H3" t="n" s="1">
-        <v>46143.0</v>
+        <v>46147.0</v>
       </c>
     </row>
     <row r="4">
@@ -330,10 +330,10 @@
         <v>37</v>
       </c>
       <c r="N7" t="n" s="2">
-        <v>46143.0</v>
+        <v>46147.0</v>
       </c>
       <c r="O7" t="n" s="3">
-        <v>46141.0</v>
+        <v>46145.0</v>
       </c>
     </row>
     <row r="8">
